--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152453</v>
+        <v>121152475</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>90853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675421</v>
+        <v>675548</v>
       </c>
       <c r="R6" t="n">
-        <v>7144210</v>
+        <v>7144090</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152475</v>
+        <v>121152453</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>78598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675548</v>
+        <v>675421</v>
       </c>
       <c r="R7" t="n">
-        <v>7144090</v>
+        <v>7144210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152471</v>
+        <v>121152477</v>
       </c>
       <c r="B3" t="n">
-        <v>74697</v>
+        <v>82385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675467</v>
+        <v>675578</v>
       </c>
       <c r="R3" t="n">
         <v>7144110</v>
@@ -900,7 +900,7 @@
         <v>121152466</v>
       </c>
       <c r="B4" t="n">
-        <v>90232</v>
+        <v>90242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152472</v>
+        <v>121152475</v>
       </c>
       <c r="B5" t="n">
-        <v>79216</v>
+        <v>90863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675503</v>
+        <v>675548</v>
       </c>
       <c r="R5" t="n">
-        <v>7144100</v>
+        <v>7144090</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152475</v>
+        <v>121152471</v>
       </c>
       <c r="B6" t="n">
-        <v>90853</v>
+        <v>74700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675548</v>
+        <v>675467</v>
       </c>
       <c r="R6" t="n">
-        <v>7144090</v>
+        <v>7144110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152453</v>
+        <v>121152210</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675421</v>
+        <v>675397</v>
       </c>
       <c r="R7" t="n">
-        <v>7144210</v>
+        <v>7144170</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152209</v>
+        <v>121152474</v>
       </c>
       <c r="B8" t="n">
-        <v>90705</v>
+        <v>90644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675398</v>
+        <v>675525</v>
       </c>
       <c r="R8" t="n">
-        <v>7144070</v>
+        <v>7144080</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152478</v>
+        <v>121152453</v>
       </c>
       <c r="B9" t="n">
-        <v>90853</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675586</v>
+        <v>675421</v>
       </c>
       <c r="R9" t="n">
-        <v>7144030</v>
+        <v>7144210</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152479</v>
+        <v>121152468</v>
       </c>
       <c r="B10" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675585</v>
+        <v>675447</v>
       </c>
       <c r="R10" t="n">
-        <v>7144010</v>
+        <v>7144150</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152208</v>
+        <v>121152479</v>
       </c>
       <c r="B11" t="n">
-        <v>91127</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675443</v>
+        <v>675585</v>
       </c>
       <c r="R11" t="n">
-        <v>7143930</v>
+        <v>7144010</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152477</v>
+        <v>121152467</v>
       </c>
       <c r="B12" t="n">
-        <v>82382</v>
+        <v>92008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675578</v>
+        <v>675535</v>
       </c>
       <c r="R12" t="n">
-        <v>7144110</v>
+        <v>7144040</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152474</v>
+        <v>121152472</v>
       </c>
       <c r="B13" t="n">
-        <v>90634</v>
+        <v>79219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675525</v>
+        <v>675503</v>
       </c>
       <c r="R13" t="n">
-        <v>7144080</v>
+        <v>7144100</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152210</v>
+        <v>121152209</v>
       </c>
       <c r="B14" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675397</v>
+        <v>675398</v>
       </c>
       <c r="R14" t="n">
-        <v>7144170</v>
+        <v>7144070</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152467</v>
+        <v>121152478</v>
       </c>
       <c r="B15" t="n">
-        <v>91998</v>
+        <v>90863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675535</v>
+        <v>675586</v>
       </c>
       <c r="R15" t="n">
-        <v>7144040</v>
+        <v>7144030</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152468</v>
+        <v>121152208</v>
       </c>
       <c r="B16" t="n">
-        <v>57364</v>
+        <v>91137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,25 +2241,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675447</v>
+        <v>675443</v>
       </c>
       <c r="R16" t="n">
-        <v>7144150</v>
+        <v>7143930</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152477</v>
+        <v>121152468</v>
       </c>
       <c r="B3" t="n">
-        <v>82385</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675578</v>
+        <v>675447</v>
       </c>
       <c r="R3" t="n">
-        <v>7144110</v>
+        <v>7144150</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152466</v>
+        <v>121152472</v>
       </c>
       <c r="B4" t="n">
-        <v>90242</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675589</v>
+        <v>675503</v>
       </c>
       <c r="R4" t="n">
-        <v>7144030</v>
+        <v>7144100</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152475</v>
+        <v>121152453</v>
       </c>
       <c r="B5" t="n">
-        <v>90863</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675548</v>
+        <v>675421</v>
       </c>
       <c r="R5" t="n">
-        <v>7144090</v>
+        <v>7144210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152471</v>
+        <v>121152466</v>
       </c>
       <c r="B6" t="n">
-        <v>74700</v>
+        <v>90242</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675467</v>
+        <v>675589</v>
       </c>
       <c r="R6" t="n">
-        <v>7144110</v>
+        <v>7144030</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152210</v>
+        <v>121152474</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675397</v>
+        <v>675525</v>
       </c>
       <c r="R7" t="n">
-        <v>7144170</v>
+        <v>7144080</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152474</v>
+        <v>121152471</v>
       </c>
       <c r="B8" t="n">
-        <v>90644</v>
+        <v>74700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675525</v>
+        <v>675467</v>
       </c>
       <c r="R8" t="n">
-        <v>7144080</v>
+        <v>7144110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152453</v>
+        <v>121152209</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675421</v>
+        <v>675398</v>
       </c>
       <c r="R9" t="n">
-        <v>7144210</v>
+        <v>7144070</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152468</v>
+        <v>121152478</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>90863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675447</v>
+        <v>675586</v>
       </c>
       <c r="R10" t="n">
-        <v>7144150</v>
+        <v>7144030</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152479</v>
+        <v>121152477</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>82385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675585</v>
+        <v>675578</v>
       </c>
       <c r="R11" t="n">
-        <v>7144010</v>
+        <v>7144110</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152467</v>
+        <v>121152208</v>
       </c>
       <c r="B12" t="n">
-        <v>92008</v>
+        <v>91137</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675535</v>
+        <v>675443</v>
       </c>
       <c r="R12" t="n">
-        <v>7144040</v>
+        <v>7143930</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152472</v>
+        <v>121152475</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>90863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675503</v>
+        <v>675548</v>
       </c>
       <c r="R13" t="n">
-        <v>7144100</v>
+        <v>7144090</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152209</v>
+        <v>121152467</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>92008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675398</v>
+        <v>675535</v>
       </c>
       <c r="R14" t="n">
-        <v>7144070</v>
+        <v>7144040</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152478</v>
+        <v>121152210</v>
       </c>
       <c r="B15" t="n">
-        <v>90863</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675586</v>
+        <v>675397</v>
       </c>
       <c r="R15" t="n">
-        <v>7144030</v>
+        <v>7144170</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152208</v>
+        <v>121152479</v>
       </c>
       <c r="B16" t="n">
-        <v>91137</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,25 +2241,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675443</v>
+        <v>675585</v>
       </c>
       <c r="R16" t="n">
-        <v>7143930</v>
+        <v>7144010</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152468</v>
+        <v>121152478</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>90875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675447</v>
+        <v>675586</v>
       </c>
       <c r="R3" t="n">
-        <v>7144150</v>
+        <v>7144030</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152472</v>
+        <v>121152466</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>90254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675503</v>
+        <v>675589</v>
       </c>
       <c r="R4" t="n">
-        <v>7144100</v>
+        <v>7144030</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152453</v>
+        <v>121152467</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675421</v>
+        <v>675535</v>
       </c>
       <c r="R5" t="n">
-        <v>7144210</v>
+        <v>7144040</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152466</v>
+        <v>121152477</v>
       </c>
       <c r="B6" t="n">
-        <v>90242</v>
+        <v>82388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675589</v>
+        <v>675578</v>
       </c>
       <c r="R6" t="n">
-        <v>7144030</v>
+        <v>7144110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152474</v>
+        <v>121152453</v>
       </c>
       <c r="B7" t="n">
-        <v>90644</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675525</v>
+        <v>675421</v>
       </c>
       <c r="R7" t="n">
-        <v>7144080</v>
+        <v>7144210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152471</v>
+        <v>121152472</v>
       </c>
       <c r="B8" t="n">
-        <v>74700</v>
+        <v>79222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675467</v>
+        <v>675503</v>
       </c>
       <c r="R8" t="n">
-        <v>7144110</v>
+        <v>7144100</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152209</v>
+        <v>121152468</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675398</v>
+        <v>675447</v>
       </c>
       <c r="R9" t="n">
-        <v>7144070</v>
+        <v>7144150</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152478</v>
+        <v>121152479</v>
       </c>
       <c r="B10" t="n">
-        <v>90863</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675586</v>
+        <v>675585</v>
       </c>
       <c r="R10" t="n">
-        <v>7144030</v>
+        <v>7144010</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152477</v>
+        <v>121152475</v>
       </c>
       <c r="B11" t="n">
-        <v>82385</v>
+        <v>90875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675578</v>
+        <v>675548</v>
       </c>
       <c r="R11" t="n">
-        <v>7144110</v>
+        <v>7144090</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1788,7 +1788,7 @@
         <v>121152208</v>
       </c>
       <c r="B12" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152475</v>
+        <v>121152471</v>
       </c>
       <c r="B13" t="n">
-        <v>90863</v>
+        <v>74702</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1588</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675548</v>
+        <v>675467</v>
       </c>
       <c r="R13" t="n">
-        <v>7144090</v>
+        <v>7144110</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152467</v>
+        <v>121152210</v>
       </c>
       <c r="B14" t="n">
-        <v>92008</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675535</v>
+        <v>675397</v>
       </c>
       <c r="R14" t="n">
-        <v>7144040</v>
+        <v>7144170</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152210</v>
+        <v>121152474</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>90656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675397</v>
+        <v>675525</v>
       </c>
       <c r="R15" t="n">
-        <v>7144170</v>
+        <v>7144080</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152479</v>
+        <v>121152209</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>90727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675585</v>
+        <v>675398</v>
       </c>
       <c r="R16" t="n">
-        <v>7144010</v>
+        <v>7144070</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152478</v>
+        <v>121152472</v>
       </c>
       <c r="B3" t="n">
-        <v>90875</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675586</v>
+        <v>675503</v>
       </c>
       <c r="R3" t="n">
-        <v>7144030</v>
+        <v>7144100</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152466</v>
+        <v>121152474</v>
       </c>
       <c r="B4" t="n">
-        <v>90254</v>
+        <v>90657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675589</v>
+        <v>675525</v>
       </c>
       <c r="R4" t="n">
-        <v>7144030</v>
+        <v>7144080</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152467</v>
+        <v>121152477</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>82388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675535</v>
+        <v>675578</v>
       </c>
       <c r="R5" t="n">
-        <v>7144040</v>
+        <v>7144110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152477</v>
+        <v>121152471</v>
       </c>
       <c r="B6" t="n">
-        <v>82388</v>
+        <v>74702</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675578</v>
+        <v>675467</v>
       </c>
       <c r="R6" t="n">
         <v>7144110</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152453</v>
+        <v>121152210</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675421</v>
+        <v>675397</v>
       </c>
       <c r="R7" t="n">
-        <v>7144210</v>
+        <v>7144170</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152472</v>
+        <v>121152468</v>
       </c>
       <c r="B8" t="n">
-        <v>79222</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675503</v>
+        <v>675447</v>
       </c>
       <c r="R8" t="n">
-        <v>7144100</v>
+        <v>7144150</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152468</v>
+        <v>121152208</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>91150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675447</v>
+        <v>675443</v>
       </c>
       <c r="R9" t="n">
-        <v>7144150</v>
+        <v>7143930</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152479</v>
+        <v>121152453</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675585</v>
+        <v>675421</v>
       </c>
       <c r="R10" t="n">
-        <v>7144010</v>
+        <v>7144210</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152475</v>
+        <v>121152466</v>
       </c>
       <c r="B11" t="n">
-        <v>90875</v>
+        <v>90255</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1588</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675548</v>
+        <v>675589</v>
       </c>
       <c r="R11" t="n">
-        <v>7144090</v>
+        <v>7144030</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152208</v>
+        <v>121152467</v>
       </c>
       <c r="B12" t="n">
-        <v>91149</v>
+        <v>92021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675443</v>
+        <v>675535</v>
       </c>
       <c r="R12" t="n">
-        <v>7143930</v>
+        <v>7144040</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152471</v>
+        <v>121152475</v>
       </c>
       <c r="B13" t="n">
-        <v>74702</v>
+        <v>90876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675467</v>
+        <v>675548</v>
       </c>
       <c r="R13" t="n">
-        <v>7144110</v>
+        <v>7144090</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152210</v>
+        <v>121152479</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675397</v>
+        <v>675585</v>
       </c>
       <c r="R14" t="n">
-        <v>7144170</v>
+        <v>7144010</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152474</v>
+        <v>121152209</v>
       </c>
       <c r="B15" t="n">
-        <v>90656</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675525</v>
+        <v>675398</v>
       </c>
       <c r="R15" t="n">
-        <v>7144080</v>
+        <v>7144070</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152209</v>
+        <v>121152478</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>90876</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675398</v>
+        <v>675586</v>
       </c>
       <c r="R16" t="n">
-        <v>7144070</v>
+        <v>7144030</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152472</v>
+        <v>121152479</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675503</v>
+        <v>675585</v>
       </c>
       <c r="R3" t="n">
-        <v>7144100</v>
+        <v>7144010</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152474</v>
+        <v>121152471</v>
       </c>
       <c r="B4" t="n">
-        <v>90657</v>
+        <v>74705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675525</v>
+        <v>675467</v>
       </c>
       <c r="R4" t="n">
-        <v>7144080</v>
+        <v>7144110</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152477</v>
+        <v>121152209</v>
       </c>
       <c r="B5" t="n">
-        <v>82388</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675578</v>
+        <v>675398</v>
       </c>
       <c r="R5" t="n">
-        <v>7144110</v>
+        <v>7144070</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152471</v>
+        <v>121152210</v>
       </c>
       <c r="B6" t="n">
-        <v>74702</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675467</v>
+        <v>675397</v>
       </c>
       <c r="R6" t="n">
-        <v>7144110</v>
+        <v>7144170</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152210</v>
+        <v>121152478</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675397</v>
+        <v>675586</v>
       </c>
       <c r="R7" t="n">
-        <v>7144170</v>
+        <v>7144030</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152468</v>
+        <v>121152467</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>92024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675447</v>
+        <v>675535</v>
       </c>
       <c r="R8" t="n">
-        <v>7144150</v>
+        <v>7144040</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152208</v>
+        <v>121152477</v>
       </c>
       <c r="B9" t="n">
-        <v>91150</v>
+        <v>82391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675443</v>
+        <v>675578</v>
       </c>
       <c r="R9" t="n">
-        <v>7143930</v>
+        <v>7144110</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152453</v>
+        <v>121152208</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>91153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675421</v>
+        <v>675443</v>
       </c>
       <c r="R10" t="n">
-        <v>7144210</v>
+        <v>7143930</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152466</v>
+        <v>121152474</v>
       </c>
       <c r="B11" t="n">
-        <v>90255</v>
+        <v>90660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5754</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675589</v>
+        <v>675525</v>
       </c>
       <c r="R11" t="n">
-        <v>7144030</v>
+        <v>7144080</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152467</v>
+        <v>121152468</v>
       </c>
       <c r="B12" t="n">
-        <v>92021</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675535</v>
+        <v>675447</v>
       </c>
       <c r="R12" t="n">
-        <v>7144040</v>
+        <v>7144150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152475</v>
+        <v>121152472</v>
       </c>
       <c r="B13" t="n">
-        <v>90876</v>
+        <v>79225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675548</v>
+        <v>675503</v>
       </c>
       <c r="R13" t="n">
-        <v>7144090</v>
+        <v>7144100</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152479</v>
+        <v>121152453</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675585</v>
+        <v>675421</v>
       </c>
       <c r="R14" t="n">
-        <v>7144010</v>
+        <v>7144210</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152209</v>
+        <v>121152466</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>90258</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675398</v>
+        <v>675589</v>
       </c>
       <c r="R15" t="n">
-        <v>7144070</v>
+        <v>7144030</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152478</v>
+        <v>121152475</v>
       </c>
       <c r="B16" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675586</v>
+        <v>675548</v>
       </c>
       <c r="R16" t="n">
-        <v>7144030</v>
+        <v>7144090</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152479</v>
+        <v>121152478</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>90879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675585</v>
+        <v>675586</v>
       </c>
       <c r="R3" t="n">
-        <v>7144010</v>
+        <v>7144030</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152209</v>
+        <v>121152467</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675398</v>
+        <v>675535</v>
       </c>
       <c r="R5" t="n">
-        <v>7144070</v>
+        <v>7144040</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152210</v>
+        <v>121152479</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675397</v>
+        <v>675585</v>
       </c>
       <c r="R6" t="n">
-        <v>7144170</v>
+        <v>7144010</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152478</v>
+        <v>121152474</v>
       </c>
       <c r="B7" t="n">
-        <v>90879</v>
+        <v>90660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675586</v>
+        <v>675525</v>
       </c>
       <c r="R7" t="n">
-        <v>7144030</v>
+        <v>7144080</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152467</v>
+        <v>121152466</v>
       </c>
       <c r="B8" t="n">
-        <v>92024</v>
+        <v>90258</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675535</v>
+        <v>675589</v>
       </c>
       <c r="R8" t="n">
-        <v>7144040</v>
+        <v>7144030</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152477</v>
+        <v>121152475</v>
       </c>
       <c r="B9" t="n">
-        <v>82391</v>
+        <v>90879</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675578</v>
+        <v>675548</v>
       </c>
       <c r="R9" t="n">
-        <v>7144110</v>
+        <v>7144090</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152208</v>
+        <v>121152453</v>
       </c>
       <c r="B10" t="n">
-        <v>91153</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675443</v>
+        <v>675421</v>
       </c>
       <c r="R10" t="n">
-        <v>7143930</v>
+        <v>7144210</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152474</v>
+        <v>121152210</v>
       </c>
       <c r="B11" t="n">
-        <v>90660</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675525</v>
+        <v>675397</v>
       </c>
       <c r="R11" t="n">
-        <v>7144080</v>
+        <v>7144170</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152468</v>
+        <v>121152208</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>91153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675447</v>
+        <v>675443</v>
       </c>
       <c r="R12" t="n">
-        <v>7144150</v>
+        <v>7143930</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152472</v>
+        <v>121152209</v>
       </c>
       <c r="B13" t="n">
-        <v>79225</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675503</v>
+        <v>675398</v>
       </c>
       <c r="R13" t="n">
-        <v>7144100</v>
+        <v>7144070</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152453</v>
+        <v>121152468</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675421</v>
+        <v>675447</v>
       </c>
       <c r="R14" t="n">
-        <v>7144210</v>
+        <v>7144150</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152466</v>
+        <v>121152477</v>
       </c>
       <c r="B15" t="n">
-        <v>90258</v>
+        <v>82391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5754</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675589</v>
+        <v>675578</v>
       </c>
       <c r="R15" t="n">
-        <v>7144030</v>
+        <v>7144110</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152475</v>
+        <v>121152472</v>
       </c>
       <c r="B16" t="n">
-        <v>90879</v>
+        <v>79225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675548</v>
+        <v>675503</v>
       </c>
       <c r="R16" t="n">
-        <v>7144090</v>
+        <v>7144100</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 55308-2024 artfynd.xlsx
+++ b/artfynd/A 55308-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152471</v>
+        <v>121152467</v>
       </c>
       <c r="B4" t="n">
-        <v>74705</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675467</v>
+        <v>675535</v>
       </c>
       <c r="R4" t="n">
-        <v>7144110</v>
+        <v>7144040</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152467</v>
+        <v>121152479</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675535</v>
+        <v>675585</v>
       </c>
       <c r="R5" t="n">
-        <v>7144040</v>
+        <v>7144010</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152479</v>
+        <v>121152471</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>74705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675585</v>
+        <v>675467</v>
       </c>
       <c r="R6" t="n">
-        <v>7144010</v>
+        <v>7144110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152453</v>
+        <v>121152210</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675421</v>
+        <v>675397</v>
       </c>
       <c r="R10" t="n">
-        <v>7144210</v>
+        <v>7144170</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152210</v>
+        <v>121152208</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675397</v>
+        <v>675443</v>
       </c>
       <c r="R11" t="n">
-        <v>7144170</v>
+        <v>7143930</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152208</v>
+        <v>121152453</v>
       </c>
       <c r="B12" t="n">
-        <v>91153</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675443</v>
+        <v>675421</v>
       </c>
       <c r="R12" t="n">
-        <v>7143930</v>
+        <v>7144210</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
